--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,12 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>105657</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718615.7373742601</v>
+        <v>718616</v>
       </c>
       <c r="R11" t="n">
-        <v>6420035.284315288</v>
+        <v>6420035</v>
       </c>
       <c r="S11" t="n">
         <v>71</v>
@@ -1757,19 +1752,9 @@
           <t>1992-06-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1992-06-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1828,12 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718515.4045271697</v>
+        <v>718515</v>
       </c>
       <c r="R12" t="n">
-        <v>6420034.075958089</v>
+        <v>6420034</v>
       </c>
       <c r="S12" t="n">
         <v>71</v>
@@ -1898,19 +1878,9 @@
           <t>1992-06-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>1992-06-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1954,12 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718515.4045271697</v>
+        <v>718515</v>
       </c>
       <c r="R13" t="n">
-        <v>6420034.075958089</v>
+        <v>6420034</v>
       </c>
       <c r="S13" t="n">
         <v>71</v>
@@ -2024,19 +1989,9 @@
           <t>1992-06-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>1992-06-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108087</v>
+        <v>108096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101665</v>
+        <v>101673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101649</v>
+        <v>101657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108096</v>
+        <v>108109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101673</v>
+        <v>101678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101657</v>
+        <v>101662</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108109</v>
+        <v>108118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101662</v>
+        <v>101668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108118</v>
+        <v>108123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101668</v>
+        <v>101669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108123</v>
+        <v>108151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101669</v>
+        <v>101696</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108151</v>
+        <v>108157</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101696</v>
+        <v>101702</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108157</v>
+        <v>108164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101702</v>
+        <v>101709</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108164</v>
+        <v>108168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101709</v>
+        <v>101713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108168</v>
+        <v>108176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101713</v>
+        <v>101720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108179</v>
+        <v>108184</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101723</v>
+        <v>101728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -1687,7 +1687,7 @@
         <v>106574462</v>
       </c>
       <c r="B11" t="n">
-        <v>108184</v>
+        <v>108192</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>106583026</v>
       </c>
       <c r="B12" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>106583027</v>
       </c>
       <c r="B13" t="n">
-        <v>101728</v>
+        <v>101736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>94594174</v>
       </c>
       <c r="B2" t="n">
-        <v>76921</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718185.7403045814</v>
+        <v>718186</v>
       </c>
       <c r="R2" t="n">
-        <v>6419831.151972989</v>
+        <v>6419831</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-05-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94594047</v>
+        <v>96784261</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>3599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Narrspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cortinarius pseudoarcuatorum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Rob.Henry</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718180.4621102845</v>
+        <v>718191</v>
       </c>
       <c r="R3" t="n">
-        <v>6419869.243295882</v>
+        <v>6419909</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +851,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,37 +870,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94594259</v>
+        <v>96785366</v>
       </c>
       <c r="B4" t="n">
-        <v>5410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105894</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Smedbock</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ergates faber</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1761)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718235.7932127529</v>
+        <v>718248</v>
       </c>
       <c r="R4" t="n">
-        <v>6419833.877419001</v>
+        <v>6419989</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,22 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96784266</v>
+        <v>96785367</v>
       </c>
       <c r="B5" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +978,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718251.5349028955</v>
+        <v>718322</v>
       </c>
       <c r="R5" t="n">
-        <v>6419937.077210406</v>
+        <v>6420041</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,19 +1035,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96784030</v>
+        <v>96785368</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718294.0576142668</v>
+        <v>718271</v>
       </c>
       <c r="R6" t="n">
-        <v>6419901.548234827</v>
+        <v>6420055</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,19 +1132,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96785366</v>
+        <v>96784250</v>
       </c>
       <c r="B7" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3674</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718248.1658822938</v>
+        <v>718198</v>
       </c>
       <c r="R7" t="n">
-        <v>6419989.130045149</v>
+        <v>6419954</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1308,19 +1229,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1258,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96785367</v>
+        <v>96784030</v>
       </c>
       <c r="B8" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3674</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718322.233773072</v>
+        <v>718294</v>
       </c>
       <c r="R8" t="n">
-        <v>6420041.136342316</v>
+        <v>6419902</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1420,19 +1326,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1355,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96784261</v>
+        <v>94594259</v>
       </c>
       <c r="B9" t="n">
-        <v>85264</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3599</v>
+        <v>105894</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Narrspindling</t>
+          <t>Smedbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius pseudoarcuatorum</t>
+          <t>Ergates faber</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Rob. Henry</t>
+          <t>(Linnaeus, 1761)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718191.1001458563</v>
+        <v>718236</v>
       </c>
       <c r="R9" t="n">
-        <v>6419909.266886983</v>
+        <v>6419834</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1529,22 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,7 +1434,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1572,37 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96785007</v>
+        <v>96784266</v>
       </c>
       <c r="B10" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6003295</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1612,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718212.4394120207</v>
+        <v>718252</v>
       </c>
       <c r="R10" t="n">
-        <v>6419870.451375012</v>
+        <v>6419937</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1645,19 +1520,9 @@
           <t>2021-09-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,48 +1549,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106574462</v>
+        <v>94594047</v>
       </c>
       <c r="B11" t="n">
-        <v>108192</v>
+        <v>110078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>231568</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lansettfibbla</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hieracium caliginosum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dahlst.) Brenner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tajnungs 1500 m NNO till N, Gtl</t>
+          <t>Lilla Häftings, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718616</v>
+        <v>718181</v>
       </c>
       <c r="R11" t="n">
-        <v>6420035</v>
+        <v>6419869</v>
       </c>
       <c r="S11" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,17 +1614,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>1992-06-14</t>
+          <t>2021-05-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1992-06-14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>. Hieracium caliginosum, det. T. Tyler 2001 (i S)</t>
+          <t>2021-06-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,67 +1630,43 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Tallskog, örtrik.</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>92081</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Torbjörn Tyler</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106583026</v>
+        <v>106583027</v>
       </c>
       <c r="B12" t="n">
-        <v>101752</v>
+        <v>102225</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>221223</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1921,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>106583027</v>
+        <v>106583026</v>
       </c>
       <c r="B13" t="n">
-        <v>101736</v>
+        <v>102241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1932,16 +1768,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221223</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2029,6 +1865,229 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>106574462</v>
+      </c>
+      <c r="B14" t="n">
+        <v>108734</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>231568</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lansettfibbla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hieracium caliginosum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dahlst.) Brenner</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tajnungs 1500 m NNO till N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>718616</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6420035</v>
+      </c>
+      <c r="S14" t="n">
+        <v>71</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1992-06-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1992-06-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>. Hieracium caliginosum, det. T. Tyler 2001 (i S)</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Tallskog, örtrik.</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>92081</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Thomas Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>96785007</v>
+      </c>
+      <c r="B15" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lilla Häftings, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>718213</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6419871</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hangvar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6052-2024 artfynd.xlsx
+++ b/artfynd/A 6052-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94594174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96784261</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785366</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785367</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785368</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96784250</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96784030</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94594259</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96784266</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94594047</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106583027</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1865,6 +1925,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106583026</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1991,6 +2056,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106574462</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,8 +2158,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96785007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>